--- a/data/trans_orig/IP11A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11A-Habitat-trans_orig.xlsx
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>743</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -4626,47 +4626,47 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>5179</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4930,49 +4930,49 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t>15066</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>42,67%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>15188</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>43,02%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>9944</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>21,37%</t>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -7091,12 +7091,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9476,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>61194</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>35053</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10686,12 +10686,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11539,12 +11539,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -11750,12 +11750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11948,12 +11948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -12658,12 +12658,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -13375,12 +13375,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13390,12 +13390,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -13488,12 +13488,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -13601,12 +13601,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13636,12 +13636,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14150,12 +14150,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14205,12 +14205,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -14248,12 +14248,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14263,12 +14263,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14361,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14396,12 +14396,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14411,12 +14411,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14524,12 +14524,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14544,12 +14544,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14559,12 +14559,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -14587,12 +14587,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14672,12 +14672,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -15571,12 +15571,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -15586,12 +15586,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16268,12 +16268,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>389</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17254,12 +17254,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17274,12 +17274,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17289,12 +17289,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -17317,12 +17317,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>370</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -17332,12 +17332,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -17372,7 +17372,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17387,12 +17387,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -17402,12 +17402,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -17430,12 +17430,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17500,12 +17500,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17515,12 +17515,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17578,12 +17578,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -17593,12 +17593,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -17613,12 +17613,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -17628,12 +17628,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18187,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -18260,12 +18260,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18275,12 +18275,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18295,12 +18295,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18310,12 +18310,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -18373,12 +18373,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -18388,12 +18388,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -18408,12 +18408,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -18423,12 +18423,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -18977,12 +18977,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -18992,12 +18992,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -19020,12 +19020,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19055,12 +19055,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19070,12 +19070,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19105,12 +19105,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -19133,12 +19133,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19148,12 +19148,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19168,12 +19168,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19183,12 +19183,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19203,12 +19203,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19218,12 +19218,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -19246,12 +19246,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19261,12 +19261,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19331,12 +19331,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19394,12 +19394,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19409,12 +19409,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19429,12 +19429,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19444,12 +19444,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
